--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HamZa\Desktop\student-results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE40D630-53AA-4733-8ABE-6D2AAADFADF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB770216-0508-4102-933A-64E7ACCA2113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{FEBCBEB0-D886-45B6-A7F7-37133FA29276}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="123">
   <si>
     <t>seat_number</t>
   </si>
@@ -247,6 +247,153 @@
   </si>
   <si>
     <t>الأول</t>
+  </si>
+  <si>
+    <t>ديندا ياسمين صبريا</t>
+  </si>
+  <si>
+    <t>سيتي عفيفة فوزية جمعة</t>
+  </si>
+  <si>
+    <t>فطنة إنساني</t>
+  </si>
+  <si>
+    <t>مفاتح السبيل</t>
+  </si>
+  <si>
+    <t>النساء مطمئنة</t>
+  </si>
+  <si>
+    <t>أذكياء بررة</t>
+  </si>
+  <si>
+    <t>ألفيرا مولد نصر</t>
+  </si>
+  <si>
+    <t>ريشا نور أولياء</t>
+  </si>
+  <si>
+    <t>زهوى يوسف</t>
+  </si>
+  <si>
+    <t>سيفتياني سيتي رحيمة</t>
+  </si>
+  <si>
+    <t>مورا مارفينكي</t>
+  </si>
+  <si>
+    <t>نينجروم دوي ليستاري</t>
+  </si>
+  <si>
+    <t>ييلسي</t>
+  </si>
+  <si>
+    <t>النساء أولياء نور</t>
+  </si>
+  <si>
+    <t>النساء حسن المطمئنة</t>
+  </si>
+  <si>
+    <t>النساء يوستيكا</t>
+  </si>
+  <si>
+    <t>أتني</t>
+  </si>
+  <si>
+    <t>أندارينا شهنى ممارجا</t>
+  </si>
+  <si>
+    <t>أنديني شيترا أيو</t>
+  </si>
+  <si>
+    <t>أولياء فوزية</t>
+  </si>
+  <si>
+    <t>تريسيناواتي</t>
+  </si>
+  <si>
+    <t>زهرنا فرحة مولدا</t>
+  </si>
+  <si>
+    <t>سري أيو</t>
+  </si>
+  <si>
+    <t>عفاف عزيزة</t>
+  </si>
+  <si>
+    <t>فاتحة نور سعادة</t>
+  </si>
+  <si>
+    <t>قانتة مطمئنة</t>
+  </si>
+  <si>
+    <t>نجوى شريفة أنوار</t>
+  </si>
+  <si>
+    <t>نذيرة</t>
+  </si>
+  <si>
+    <t>ألف فيبريأنتي</t>
+  </si>
+  <si>
+    <t>حنينة أسماء شهيدة</t>
+  </si>
+  <si>
+    <t>رفدا أليفية</t>
+  </si>
+  <si>
+    <t>زالفا نور فائزة</t>
+  </si>
+  <si>
+    <t>سارة النساء</t>
+  </si>
+  <si>
+    <t>فريال زهوا تذكية</t>
+  </si>
+  <si>
+    <t>كونيتا ساري نينجسيه</t>
+  </si>
+  <si>
+    <t>كيلا أماني</t>
+  </si>
+  <si>
+    <t>لطفية نور عائدة</t>
+  </si>
+  <si>
+    <t>نبيلة</t>
+  </si>
+  <si>
+    <t>صفوة الفداء كاملة يسري</t>
+  </si>
+  <si>
+    <t>هاجر سالما سلسبيل</t>
+  </si>
+  <si>
+    <t>الخنساء</t>
+  </si>
+  <si>
+    <t>إيرما رمضاني</t>
+  </si>
+  <si>
+    <t>أولياء فطرياسما نور جنة</t>
+  </si>
+  <si>
+    <t>نائلة نور اثنين</t>
+  </si>
+  <si>
+    <t>سوتشي عملية دارا سافيتري</t>
+  </si>
+  <si>
+    <t>ملكة جنة خليلة</t>
+  </si>
+  <si>
+    <t>فضيلة ليلة السعادة</t>
+  </si>
+  <si>
+    <t>النساء لَيلي ريفدا</t>
+  </si>
+  <si>
+    <t>الثالث</t>
   </si>
 </sst>
 </file>
@@ -282,9 +429,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -599,7 +745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6940186C-A40F-42B7-9FEE-B56A47B6E16E}">
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:Q105"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.90625" bestFit="1" customWidth="1"/>
@@ -660,7 +806,7 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>260711069</v>
       </c>
       <c r="B2" t="s">
@@ -674,7 +820,7 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>260711042</v>
       </c>
       <c r="B3" t="s">
@@ -688,7 +834,7 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>260711004</v>
       </c>
       <c r="B4" t="s">
@@ -702,7 +848,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>260711001</v>
       </c>
       <c r="B5" t="s">
@@ -716,7 +862,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>260711169</v>
       </c>
       <c r="B6" t="s">
@@ -730,7 +876,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
+      <c r="A7">
         <v>260711086</v>
       </c>
       <c r="B7" t="s">
@@ -744,7 +890,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>260711088</v>
       </c>
       <c r="B8" t="s">
@@ -758,7 +904,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
+      <c r="A9">
         <v>260711031</v>
       </c>
       <c r="B9" t="s">
@@ -772,7 +918,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
+      <c r="A10">
         <v>260711005</v>
       </c>
       <c r="B10" t="s">
@@ -786,7 +932,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
+      <c r="A11">
         <v>260711006</v>
       </c>
       <c r="B11" t="s">
@@ -800,7 +946,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
+      <c r="A12">
         <v>260711017</v>
       </c>
       <c r="B12" t="s">
@@ -814,7 +960,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
+      <c r="A13">
         <v>260711071</v>
       </c>
       <c r="B13" t="s">
@@ -828,7 +974,7 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
+      <c r="A14">
         <v>260711011</v>
       </c>
       <c r="B14" t="s">
@@ -842,7 +988,7 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
+      <c r="A15">
         <v>260711010</v>
       </c>
       <c r="B15" t="s">
@@ -856,7 +1002,7 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
+      <c r="A16">
         <v>260711020</v>
       </c>
       <c r="B16" t="s">
@@ -870,7 +1016,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
+      <c r="A17">
         <v>260711044</v>
       </c>
       <c r="B17" t="s">
@@ -884,7 +1030,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
+      <c r="A18">
         <v>260711096</v>
       </c>
       <c r="B18" t="s">
@@ -898,7 +1044,7 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
+      <c r="A19">
         <v>260711016</v>
       </c>
       <c r="B19" t="s">
@@ -912,7 +1058,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
+      <c r="A20">
         <v>260711032</v>
       </c>
       <c r="B20" t="s">
@@ -926,7 +1072,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
+      <c r="A21">
         <v>260711033</v>
       </c>
       <c r="B21" t="s">
@@ -940,7 +1086,7 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
+      <c r="A22">
         <v>260711022</v>
       </c>
       <c r="B22" t="s">
@@ -954,7 +1100,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
+      <c r="A23">
         <v>260711102</v>
       </c>
       <c r="B23" t="s">
@@ -968,7 +1114,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
+      <c r="A24">
         <v>260711075</v>
       </c>
       <c r="B24" t="s">
@@ -982,7 +1128,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
+      <c r="A25">
         <v>260711049</v>
       </c>
       <c r="B25" t="s">
@@ -996,7 +1142,7 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
+      <c r="A26">
         <v>260711104</v>
       </c>
       <c r="B26" t="s">
@@ -1010,7 +1156,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A27" s="1">
+      <c r="A27">
         <v>260711045</v>
       </c>
       <c r="B27" t="s">
@@ -1024,7 +1170,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A28" s="1">
+      <c r="A28">
         <v>260711084</v>
       </c>
       <c r="B28" t="s">
@@ -1038,7 +1184,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A29" s="1">
+      <c r="A29">
         <v>260711055</v>
       </c>
       <c r="B29" t="s">
@@ -1052,7 +1198,7 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
+      <c r="A30">
         <v>260711080</v>
       </c>
       <c r="B30" t="s">
@@ -1066,7 +1212,7 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A31" s="1">
+      <c r="A31">
         <v>1001001</v>
       </c>
       <c r="B31" t="s">
@@ -1080,7 +1226,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A32" s="1">
+      <c r="A32">
         <v>260711048</v>
       </c>
       <c r="B32" t="s">
@@ -1094,7 +1240,7 @@
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A33" s="1">
+      <c r="A33">
         <v>260711026</v>
       </c>
       <c r="B33" t="s">
@@ -1108,7 +1254,7 @@
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A34" s="1">
+      <c r="A34">
         <v>260711107</v>
       </c>
       <c r="B34" t="s">
@@ -1122,7 +1268,7 @@
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A35" s="1">
+      <c r="A35">
         <v>260711100</v>
       </c>
       <c r="B35" t="s">
@@ -1136,7 +1282,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A36" s="1">
+      <c r="A36">
         <v>260711077</v>
       </c>
       <c r="B36" t="s">
@@ -1150,7 +1296,7 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A37" s="1">
+      <c r="A37">
         <v>260711082</v>
       </c>
       <c r="B37" t="s">
@@ -1164,7 +1310,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A38" s="1">
+      <c r="A38">
         <v>260711052</v>
       </c>
       <c r="B38" t="s">
@@ -1178,7 +1324,7 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A39" s="1">
+      <c r="A39">
         <v>260711051</v>
       </c>
       <c r="B39" t="s">
@@ -1192,7 +1338,7 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A40" s="1">
+      <c r="A40">
         <v>260711078</v>
       </c>
       <c r="B40" t="s">
@@ -1206,7 +1352,7 @@
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A41" s="1">
+      <c r="A41">
         <v>260711027</v>
       </c>
       <c r="B41" t="s">
@@ -1220,7 +1366,7 @@
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A42" s="1">
+      <c r="A42">
         <v>260711028</v>
       </c>
       <c r="B42" t="s">
@@ -1234,7 +1380,7 @@
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A43" s="1">
+      <c r="A43">
         <v>260711111</v>
       </c>
       <c r="B43" t="s">
@@ -1248,7 +1394,7 @@
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A44" s="1">
+      <c r="A44">
         <v>260711038</v>
       </c>
       <c r="B44" t="s">
@@ -1262,7 +1408,7 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A45" s="1">
+      <c r="A45">
         <v>260711090</v>
       </c>
       <c r="B45" t="s">
@@ -1276,7 +1422,7 @@
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A46" s="1">
+      <c r="A46">
         <v>260711062</v>
       </c>
       <c r="B46" t="s">
@@ -1290,7 +1436,7 @@
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A47" s="1">
+      <c r="A47">
         <v>260711064</v>
       </c>
       <c r="B47" t="s">
@@ -1304,7 +1450,7 @@
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A48" s="1">
+      <c r="A48">
         <v>260711041</v>
       </c>
       <c r="B48" t="s">
@@ -1318,7 +1464,7 @@
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A49" s="1">
+      <c r="A49">
         <v>260711040</v>
       </c>
       <c r="B49" t="s">
@@ -1332,7 +1478,7 @@
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A50" s="1">
+      <c r="A50">
         <v>260711013</v>
       </c>
       <c r="B50" t="s">
@@ -1346,7 +1492,7 @@
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A51" s="1">
+      <c r="A51">
         <v>260711067</v>
       </c>
       <c r="B51" t="s">
@@ -1360,7 +1506,7 @@
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A52" s="1">
+      <c r="A52">
         <v>260711014</v>
       </c>
       <c r="B52" t="s">
@@ -1374,7 +1520,7 @@
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A53" s="1">
+      <c r="A53">
         <v>260711018</v>
       </c>
       <c r="B53" t="s">
@@ -1388,7 +1534,7 @@
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A54" s="1">
+      <c r="A54">
         <v>260711056</v>
       </c>
       <c r="B54" t="s">
@@ -1402,7 +1548,7 @@
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A55" s="1">
+      <c r="A55">
         <v>260711171</v>
       </c>
       <c r="B55" t="s">
@@ -1416,7 +1562,7 @@
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A56" s="1">
+      <c r="A56">
         <v>260711061</v>
       </c>
       <c r="B56" t="s">
@@ -1441,6 +1587,822 @@
       </c>
       <c r="K57">
         <v>28</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>250611045</v>
+      </c>
+      <c r="B58" t="s">
+        <v>114</v>
+      </c>
+      <c r="C58" t="s">
+        <v>122</v>
+      </c>
+      <c r="D58">
+        <v>56</v>
+      </c>
+      <c r="E58">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>250611052</v>
+      </c>
+      <c r="B59" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" t="s">
+        <v>122</v>
+      </c>
+      <c r="D59">
+        <v>58</v>
+      </c>
+      <c r="E59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>250611048</v>
+      </c>
+      <c r="B60" t="s">
+        <v>88</v>
+      </c>
+      <c r="C60" t="s">
+        <v>122</v>
+      </c>
+      <c r="D60">
+        <v>57</v>
+      </c>
+      <c r="E60">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>250611055</v>
+      </c>
+      <c r="B61" t="s">
+        <v>121</v>
+      </c>
+      <c r="C61" t="s">
+        <v>122</v>
+      </c>
+      <c r="D61">
+        <v>56</v>
+      </c>
+      <c r="E61">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>250611054</v>
+      </c>
+      <c r="B62" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" t="s">
+        <v>122</v>
+      </c>
+      <c r="D62">
+        <v>57</v>
+      </c>
+      <c r="E62">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>250611051</v>
+      </c>
+      <c r="B63" t="s">
+        <v>89</v>
+      </c>
+      <c r="C63" t="s">
+        <v>122</v>
+      </c>
+      <c r="D63">
+        <v>56</v>
+      </c>
+      <c r="E63">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>250611065</v>
+      </c>
+      <c r="B64" t="s">
+        <v>115</v>
+      </c>
+      <c r="C64" t="s">
+        <v>122</v>
+      </c>
+      <c r="D64">
+        <v>57</v>
+      </c>
+      <c r="E64">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>250611056</v>
+      </c>
+      <c r="B65" t="s">
+        <v>90</v>
+      </c>
+      <c r="C65" t="s">
+        <v>122</v>
+      </c>
+      <c r="D65">
+        <v>58</v>
+      </c>
+      <c r="E65">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>250611042</v>
+      </c>
+      <c r="B66" t="s">
+        <v>79</v>
+      </c>
+      <c r="C66" t="s">
+        <v>122</v>
+      </c>
+      <c r="D66">
+        <v>59</v>
+      </c>
+      <c r="E66">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>250611046</v>
+      </c>
+      <c r="B67" t="s">
+        <v>102</v>
+      </c>
+      <c r="C67" t="s">
+        <v>122</v>
+      </c>
+      <c r="D67">
+        <v>57</v>
+      </c>
+      <c r="E67">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>250611047</v>
+      </c>
+      <c r="B68" t="s">
+        <v>80</v>
+      </c>
+      <c r="C68" t="s">
+        <v>122</v>
+      </c>
+      <c r="D68">
+        <v>59</v>
+      </c>
+      <c r="E68">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>250611049</v>
+      </c>
+      <c r="B69" t="s">
+        <v>91</v>
+      </c>
+      <c r="C69" t="s">
+        <v>122</v>
+      </c>
+      <c r="D69">
+        <v>57</v>
+      </c>
+      <c r="E69">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>250611050</v>
+      </c>
+      <c r="B70" t="s">
+        <v>92</v>
+      </c>
+      <c r="C70" t="s">
+        <v>122</v>
+      </c>
+      <c r="D70">
+        <v>56</v>
+      </c>
+      <c r="E70">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>250611058</v>
+      </c>
+      <c r="B71" t="s">
+        <v>116</v>
+      </c>
+      <c r="C71" t="s">
+        <v>122</v>
+      </c>
+      <c r="D71">
+        <v>57</v>
+      </c>
+      <c r="E71">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>250611057</v>
+      </c>
+      <c r="B72" t="s">
+        <v>93</v>
+      </c>
+      <c r="C72" t="s">
+        <v>122</v>
+      </c>
+      <c r="D72">
+        <v>58</v>
+      </c>
+      <c r="E72">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>250611090</v>
+      </c>
+      <c r="B73" t="s">
+        <v>94</v>
+      </c>
+      <c r="C73" t="s">
+        <v>122</v>
+      </c>
+      <c r="D73">
+        <v>56</v>
+      </c>
+      <c r="E73">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>250611064</v>
+      </c>
+      <c r="B74" t="s">
+        <v>103</v>
+      </c>
+      <c r="C74" t="s">
+        <v>122</v>
+      </c>
+      <c r="D74">
+        <v>57</v>
+      </c>
+      <c r="E74">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>250611059</v>
+      </c>
+      <c r="B75" t="s">
+        <v>74</v>
+      </c>
+      <c r="C75" t="s">
+        <v>122</v>
+      </c>
+      <c r="D75">
+        <v>59</v>
+      </c>
+      <c r="E75">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>250611083</v>
+      </c>
+      <c r="B76" t="s">
+        <v>104</v>
+      </c>
+      <c r="C76" t="s">
+        <v>122</v>
+      </c>
+      <c r="D76">
+        <v>56</v>
+      </c>
+      <c r="E76">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>250611084</v>
+      </c>
+      <c r="B77" t="s">
+        <v>81</v>
+      </c>
+      <c r="C77" t="s">
+        <v>122</v>
+      </c>
+      <c r="D77">
+        <v>58</v>
+      </c>
+      <c r="E77">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>250611095</v>
+      </c>
+      <c r="B78" t="s">
+        <v>105</v>
+      </c>
+      <c r="C78" t="s">
+        <v>122</v>
+      </c>
+      <c r="D78">
+        <v>57</v>
+      </c>
+      <c r="E78">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>250611093</v>
+      </c>
+      <c r="B79" t="s">
+        <v>95</v>
+      </c>
+      <c r="C79" t="s">
+        <v>122</v>
+      </c>
+      <c r="D79">
+        <v>57</v>
+      </c>
+      <c r="E79">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>250611094</v>
+      </c>
+      <c r="B80" t="s">
+        <v>82</v>
+      </c>
+      <c r="C80" t="s">
+        <v>122</v>
+      </c>
+      <c r="D80">
+        <v>58</v>
+      </c>
+      <c r="E80">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>250611085</v>
+      </c>
+      <c r="B81" t="s">
+        <v>106</v>
+      </c>
+      <c r="C81" t="s">
+        <v>122</v>
+      </c>
+      <c r="D81">
+        <v>58</v>
+      </c>
+      <c r="E81">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>250611088</v>
+      </c>
+      <c r="B82" t="s">
+        <v>96</v>
+      </c>
+      <c r="C82" t="s">
+        <v>122</v>
+      </c>
+      <c r="D82">
+        <v>59</v>
+      </c>
+      <c r="E82">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>250611089</v>
+      </c>
+      <c r="B83" t="s">
+        <v>118</v>
+      </c>
+      <c r="C83" t="s">
+        <v>122</v>
+      </c>
+      <c r="D83">
+        <v>58</v>
+      </c>
+      <c r="E83">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>250611087</v>
+      </c>
+      <c r="B84" t="s">
+        <v>75</v>
+      </c>
+      <c r="C84" t="s">
+        <v>122</v>
+      </c>
+      <c r="D84">
+        <v>58</v>
+      </c>
+      <c r="E84">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>250611086</v>
+      </c>
+      <c r="B85" t="s">
+        <v>83</v>
+      </c>
+      <c r="C85" t="s">
+        <v>122</v>
+      </c>
+      <c r="D85">
+        <v>58</v>
+      </c>
+      <c r="E85">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>240511077</v>
+      </c>
+      <c r="B86" t="s">
+        <v>112</v>
+      </c>
+      <c r="C86" t="s">
+        <v>122</v>
+      </c>
+      <c r="D86">
+        <v>58</v>
+      </c>
+      <c r="E86">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>250611043</v>
+      </c>
+      <c r="B87" t="s">
+        <v>97</v>
+      </c>
+      <c r="C87" t="s">
+        <v>122</v>
+      </c>
+      <c r="D87">
+        <v>57</v>
+      </c>
+      <c r="E87">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>250611061</v>
+      </c>
+      <c r="B88" t="s">
+        <v>98</v>
+      </c>
+      <c r="C88" t="s">
+        <v>122</v>
+      </c>
+      <c r="D88">
+        <v>56</v>
+      </c>
+      <c r="E88">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>250611062</v>
+      </c>
+      <c r="B89" t="s">
+        <v>107</v>
+      </c>
+      <c r="C89" t="s">
+        <v>122</v>
+      </c>
+      <c r="D89">
+        <v>57</v>
+      </c>
+      <c r="E89">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>250611060</v>
+      </c>
+      <c r="B90" t="s">
+        <v>120</v>
+      </c>
+      <c r="C90" t="s">
+        <v>122</v>
+      </c>
+      <c r="D90">
+        <v>55</v>
+      </c>
+      <c r="E90">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>250611081</v>
+      </c>
+      <c r="B91" t="s">
+        <v>76</v>
+      </c>
+      <c r="C91" t="s">
+        <v>122</v>
+      </c>
+      <c r="D91">
+        <v>59</v>
+      </c>
+      <c r="E91">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>250611082</v>
+      </c>
+      <c r="B92" t="s">
+        <v>99</v>
+      </c>
+      <c r="C92" t="s">
+        <v>122</v>
+      </c>
+      <c r="D92">
+        <v>57</v>
+      </c>
+      <c r="E92">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>250611070</v>
+      </c>
+      <c r="B93" t="s">
+        <v>108</v>
+      </c>
+      <c r="C93" t="s">
+        <v>122</v>
+      </c>
+      <c r="D93">
+        <v>56</v>
+      </c>
+      <c r="E93">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>250611068</v>
+      </c>
+      <c r="B94" t="s">
+        <v>109</v>
+      </c>
+      <c r="C94" t="s">
+        <v>122</v>
+      </c>
+      <c r="D94">
+        <v>58</v>
+      </c>
+      <c r="E94">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>250611071</v>
+      </c>
+      <c r="B95" t="s">
+        <v>110</v>
+      </c>
+      <c r="C95" t="s">
+        <v>122</v>
+      </c>
+      <c r="D95">
+        <v>58</v>
+      </c>
+      <c r="E95">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>250611072</v>
+      </c>
+      <c r="B96" t="s">
+        <v>77</v>
+      </c>
+      <c r="C96" t="s">
+        <v>122</v>
+      </c>
+      <c r="D96">
+        <v>59</v>
+      </c>
+      <c r="E96">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>250611073</v>
+      </c>
+      <c r="B97" t="s">
+        <v>119</v>
+      </c>
+      <c r="C97" t="s">
+        <v>122</v>
+      </c>
+      <c r="D97">
+        <v>58</v>
+      </c>
+      <c r="E97">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>250611074</v>
+      </c>
+      <c r="B98" t="s">
+        <v>84</v>
+      </c>
+      <c r="C98" t="s">
+        <v>122</v>
+      </c>
+      <c r="D98">
+        <v>58</v>
+      </c>
+      <c r="E98">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>250611077</v>
+      </c>
+      <c r="B99" t="s">
+        <v>117</v>
+      </c>
+      <c r="C99" t="s">
+        <v>122</v>
+      </c>
+      <c r="D99">
+        <v>56</v>
+      </c>
+      <c r="E99">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>250611075</v>
+      </c>
+      <c r="B100" t="s">
+        <v>111</v>
+      </c>
+      <c r="C100" t="s">
+        <v>122</v>
+      </c>
+      <c r="D100">
+        <v>57</v>
+      </c>
+      <c r="E100">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>250611076</v>
+      </c>
+      <c r="B101" t="s">
+        <v>100</v>
+      </c>
+      <c r="C101" t="s">
+        <v>122</v>
+      </c>
+      <c r="D101">
+        <v>59</v>
+      </c>
+      <c r="E101">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>250611078</v>
+      </c>
+      <c r="B102" t="s">
+        <v>101</v>
+      </c>
+      <c r="C102" t="s">
+        <v>122</v>
+      </c>
+      <c r="D102">
+        <v>58</v>
+      </c>
+      <c r="E102">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>250611079</v>
+      </c>
+      <c r="B103" t="s">
+        <v>85</v>
+      </c>
+      <c r="C103" t="s">
+        <v>122</v>
+      </c>
+      <c r="D103">
+        <v>57</v>
+      </c>
+      <c r="E103">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>250611063</v>
+      </c>
+      <c r="B104" t="s">
+        <v>113</v>
+      </c>
+      <c r="C104" t="s">
+        <v>122</v>
+      </c>
+      <c r="D104">
+        <v>57</v>
+      </c>
+      <c r="E104">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>250611091</v>
+      </c>
+      <c r="B105" t="s">
+        <v>86</v>
+      </c>
+      <c r="C105" t="s">
+        <v>122</v>
+      </c>
+      <c r="D105">
+        <v>58</v>
+      </c>
+      <c r="E105">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/students.xlsx
+++ b/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HamZa\Desktop\student-results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB770216-0508-4102-933A-64E7ACCA2113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9887FB-16E2-40A1-AB75-40226E1D3F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{FEBCBEB0-D886-45B6-A7F7-37133FA29276}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="217">
   <si>
     <t>seat_number</t>
   </si>
@@ -394,6 +394,288 @@
   </si>
   <si>
     <t>الثالث</t>
+  </si>
+  <si>
+    <t>عبد العلي هبان</t>
+  </si>
+  <si>
+    <t>عبد الغني ريحان جينار</t>
+  </si>
+  <si>
+    <t>عبد الحكيم</t>
+  </si>
+  <si>
+    <t>عفيف مناجاة</t>
+  </si>
+  <si>
+    <t>أحمد كامل بحر</t>
+  </si>
+  <si>
+    <t>أحمد شفاء</t>
+  </si>
+  <si>
+    <t>ألدوينوف أحمدي بوترا</t>
+  </si>
+  <si>
+    <t>أمر الله الحسن</t>
+  </si>
+  <si>
+    <t>أربي ريستو لاكسونو</t>
+  </si>
+  <si>
+    <t>كانتونا عبد الرحمن</t>
+  </si>
+  <si>
+    <t>دافا أسلمي برمانا</t>
+  </si>
+  <si>
+    <t>دارس محمد أفلح</t>
+  </si>
+  <si>
+    <t>فهمي هداية الله</t>
+  </si>
+  <si>
+    <t>فائز الأمم</t>
+  </si>
+  <si>
+    <t>فريد أندريان</t>
+  </si>
+  <si>
+    <t>فوز العظيم</t>
+  </si>
+  <si>
+    <t>حسبي الله</t>
+  </si>
+  <si>
+    <t>إبراهيم ابن سينا العرزو</t>
+  </si>
+  <si>
+    <t>إلياس نور فلاح</t>
+  </si>
+  <si>
+    <t>عرفان مولانا فرمانشاه</t>
+  </si>
+  <si>
+    <t>ميتا أربر</t>
+  </si>
+  <si>
+    <t>محمد حسن الأشعري</t>
+  </si>
+  <si>
+    <t>محمد غني يوسف حسني</t>
+  </si>
+  <si>
+    <t>محمد شكور</t>
+  </si>
+  <si>
+    <t>مح. فيصل أرديانشاه</t>
+  </si>
+  <si>
+    <t>محمد نبيل ماولاني</t>
+  </si>
+  <si>
+    <t>محمد ذكي حواري</t>
+  </si>
+  <si>
+    <t>محمد فرحان فردوس بن إسماعيل</t>
+  </si>
+  <si>
+    <t>محمد حذيفة الرنتيسي</t>
+  </si>
+  <si>
+    <t>محمد إحسان الحق</t>
+  </si>
+  <si>
+    <t>محمد نبيل</t>
+  </si>
+  <si>
+    <t>محمد رمضاني</t>
+  </si>
+  <si>
+    <t>محمد رزقي فضيلة</t>
+  </si>
+  <si>
+    <t>محمد يحيى</t>
+  </si>
+  <si>
+    <t>محمد زكي إبراهيم</t>
+  </si>
+  <si>
+    <t>راديتيا تافاني</t>
+  </si>
+  <si>
+    <t>رحمد سبيل الله</t>
+  </si>
+  <si>
+    <t>رزقي فضيلة ساندي</t>
+  </si>
+  <si>
+    <t>شهابي أحمد</t>
+  </si>
+  <si>
+    <t>يزيد رحمة هداية</t>
+  </si>
+  <si>
+    <t>استقامة</t>
+  </si>
+  <si>
+    <t>النساء جوليانتي</t>
+  </si>
+  <si>
+    <t>النساء هداية الله</t>
+  </si>
+  <si>
+    <t>أديرا نور فضيلة</t>
+  </si>
+  <si>
+    <t>أزكة لطفية</t>
+  </si>
+  <si>
+    <t>أم كلثوم</t>
+  </si>
+  <si>
+    <t>أنجون ديرغاهايو نورسول</t>
+  </si>
+  <si>
+    <t>إيفا أرتنتري</t>
+  </si>
+  <si>
+    <t>إيما أتما كورنياتي</t>
+  </si>
+  <si>
+    <t>بوتري سابرينا</t>
+  </si>
+  <si>
+    <t>حسن الخاتمة</t>
+  </si>
+  <si>
+    <t>رفدة فريدة</t>
+  </si>
+  <si>
+    <t>سفتينا ساري نينسيه</t>
+  </si>
+  <si>
+    <t>سلمي كافة إنساني</t>
+  </si>
+  <si>
+    <t>سيتي نور خيرية</t>
+  </si>
+  <si>
+    <t>شفاء فطرية</t>
+  </si>
+  <si>
+    <t>شنتا شهيدة شيتا</t>
+  </si>
+  <si>
+    <t>عفيفة نفيسة أمة الله</t>
+  </si>
+  <si>
+    <t>فتحية نشأة قانتة</t>
+  </si>
+  <si>
+    <t>فطري زهرة الشفاء</t>
+  </si>
+  <si>
+    <t>لطفية تشهيا إيماني</t>
+  </si>
+  <si>
+    <t>مرأة الصالحة</t>
+  </si>
+  <si>
+    <t>مرأة زكية س</t>
+  </si>
+  <si>
+    <t>مفتاح البيت</t>
+  </si>
+  <si>
+    <t>نبيلة زهرة</t>
+  </si>
+  <si>
+    <t>نجوى صراحة مسلم</t>
+  </si>
+  <si>
+    <t>نور هاليزا</t>
+  </si>
+  <si>
+    <t>نورة الفية</t>
+  </si>
+  <si>
+    <t>أزوى فيسكا الزهراء</t>
+  </si>
+  <si>
+    <t>ألف ليرضى</t>
+  </si>
+  <si>
+    <t>أليفة سَوسان رانية</t>
+  </si>
+  <si>
+    <t>أنانديا عزة بوتري ماهاراني هيرماوان</t>
+  </si>
+  <si>
+    <t>أندي مهيمنة مرزوق</t>
+  </si>
+  <si>
+    <t>تريسنا أبرياني</t>
+  </si>
+  <si>
+    <t>جابرة فتحية</t>
+  </si>
+  <si>
+    <t>جيهان فضيلة</t>
+  </si>
+  <si>
+    <t>حنيفة بوتري حيندايانا</t>
+  </si>
+  <si>
+    <t>خليصة الأصِّف</t>
+  </si>
+  <si>
+    <t>ديشا النجلاء ظاهرة</t>
+  </si>
+  <si>
+    <t>ربيعة العدوية</t>
+  </si>
+  <si>
+    <t>زيانا نجمة ثاقبة</t>
+  </si>
+  <si>
+    <t>سارة ليلى رمضاني</t>
+  </si>
+  <si>
+    <t>سسكيا زهراني</t>
+  </si>
+  <si>
+    <t>سيلينا ليسيان أودجه</t>
+  </si>
+  <si>
+    <t>شاناندا رمضاني بوتري</t>
+  </si>
+  <si>
+    <t>ضياء خفيفة الأقوى</t>
+  </si>
+  <si>
+    <t>عائشة زهرة رمضاني</t>
+  </si>
+  <si>
+    <t>علياء حوسنيتا</t>
+  </si>
+  <si>
+    <t>فريال كهيعص حافظة</t>
+  </si>
+  <si>
+    <t>ليلى شافرة فجر</t>
+  </si>
+  <si>
+    <t>نادية حسني براناتا</t>
+  </si>
+  <si>
+    <t>نجوى عريقة أول سيريغار</t>
+  </si>
+  <si>
+    <t>نور المغفرة</t>
+  </si>
+  <si>
+    <t>نيلا أردلّة</t>
   </si>
 </sst>
 </file>
@@ -429,8 +711,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -745,11 +1031,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6940186C-A40F-42B7-9FEE-B56A47B6E16E}">
-  <dimension ref="A1:Q105"/>
+  <dimension ref="A1:Q199"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
@@ -2405,6 +2692,1443 @@
         <v>59</v>
       </c>
     </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>250611001</v>
+      </c>
+      <c r="B106" t="s">
+        <v>123</v>
+      </c>
+      <c r="C106" t="s">
+        <v>122</v>
+      </c>
+      <c r="D106" s="2">
+        <v>53.222222222222221</v>
+      </c>
+      <c r="E106" s="2">
+        <v>47.80555555555555</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>250611002</v>
+      </c>
+      <c r="B107" t="s">
+        <v>124</v>
+      </c>
+      <c r="C107" t="s">
+        <v>122</v>
+      </c>
+      <c r="D107" s="2">
+        <v>50.777777777777779</v>
+      </c>
+      <c r="E107" s="2">
+        <v>44.75</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>250611003</v>
+      </c>
+      <c r="B108" t="s">
+        <v>125</v>
+      </c>
+      <c r="C108" t="s">
+        <v>122</v>
+      </c>
+      <c r="D108" s="2">
+        <v>44.333333333333336</v>
+      </c>
+      <c r="E108" s="2">
+        <v>52.472222222222221</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>250611004</v>
+      </c>
+      <c r="B109" t="s">
+        <v>126</v>
+      </c>
+      <c r="C109" t="s">
+        <v>122</v>
+      </c>
+      <c r="D109" s="2">
+        <v>58</v>
+      </c>
+      <c r="E109" s="2">
+        <v>52.527777777777779</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>250611005</v>
+      </c>
+      <c r="B110" t="s">
+        <v>127</v>
+      </c>
+      <c r="C110" t="s">
+        <v>122</v>
+      </c>
+      <c r="D110" s="2">
+        <v>36.222222222222221</v>
+      </c>
+      <c r="E110" s="2">
+        <v>49.083333333333329</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>250611007</v>
+      </c>
+      <c r="B111" t="s">
+        <v>128</v>
+      </c>
+      <c r="C111" t="s">
+        <v>122</v>
+      </c>
+      <c r="D111" s="2">
+        <v>56.444444444444443</v>
+      </c>
+      <c r="E111" s="2">
+        <v>49.555555555555557</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>250611008</v>
+      </c>
+      <c r="B112" t="s">
+        <v>129</v>
+      </c>
+      <c r="C112" t="s">
+        <v>122</v>
+      </c>
+      <c r="D112" s="2">
+        <v>45</v>
+      </c>
+      <c r="E112" s="2">
+        <v>46.055555555555557</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>250611009</v>
+      </c>
+      <c r="B113" t="s">
+        <v>130</v>
+      </c>
+      <c r="C113" t="s">
+        <v>122</v>
+      </c>
+      <c r="D113" s="2">
+        <v>58.888888888888886</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45.916666666666664</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>250611010</v>
+      </c>
+      <c r="B114" t="s">
+        <v>131</v>
+      </c>
+      <c r="C114" t="s">
+        <v>122</v>
+      </c>
+      <c r="D114" s="2">
+        <v>55.333333333333336</v>
+      </c>
+      <c r="E114" s="2">
+        <v>52.361111111111114</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>250611011</v>
+      </c>
+      <c r="B115" t="s">
+        <v>132</v>
+      </c>
+      <c r="C115" t="s">
+        <v>122</v>
+      </c>
+      <c r="D115" s="2">
+        <v>50.44444444444445</v>
+      </c>
+      <c r="E115" s="2">
+        <v>38.527777777777779</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>250611012</v>
+      </c>
+      <c r="B116" t="s">
+        <v>133</v>
+      </c>
+      <c r="C116" t="s">
+        <v>122</v>
+      </c>
+      <c r="D116" s="2">
+        <v>57.444444444444443</v>
+      </c>
+      <c r="E116" s="2">
+        <v>55.277777777777779</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>250611013</v>
+      </c>
+      <c r="B117" t="s">
+        <v>134</v>
+      </c>
+      <c r="C117" t="s">
+        <v>122</v>
+      </c>
+      <c r="D117" s="2">
+        <v>57.333333333333336</v>
+      </c>
+      <c r="E117" s="2">
+        <v>48.166666666666671</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>250611014</v>
+      </c>
+      <c r="B118" t="s">
+        <v>135</v>
+      </c>
+      <c r="C118" t="s">
+        <v>122</v>
+      </c>
+      <c r="D118" s="2">
+        <v>58.666666666666671</v>
+      </c>
+      <c r="E118" s="2">
+        <v>57.583333333333336</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>250611098</v>
+      </c>
+      <c r="B119" t="s">
+        <v>136</v>
+      </c>
+      <c r="C119" t="s">
+        <v>122</v>
+      </c>
+      <c r="D119" s="2">
+        <v>53.777777777777779</v>
+      </c>
+      <c r="E119" s="2">
+        <v>50.027777777777779</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>250611015</v>
+      </c>
+      <c r="B120" t="s">
+        <v>137</v>
+      </c>
+      <c r="C120" t="s">
+        <v>122</v>
+      </c>
+      <c r="D120" s="2">
+        <v>54.333333333333336</v>
+      </c>
+      <c r="E120" s="2">
+        <v>53.416666666666664</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>250611016</v>
+      </c>
+      <c r="B121" t="s">
+        <v>138</v>
+      </c>
+      <c r="C121" t="s">
+        <v>122</v>
+      </c>
+      <c r="D121" s="2">
+        <v>35.111111111111114</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45.468926553672318</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>250611017</v>
+      </c>
+      <c r="B122" t="s">
+        <v>139</v>
+      </c>
+      <c r="C122" t="s">
+        <v>122</v>
+      </c>
+      <c r="D122" s="2">
+        <v>56.333333333333336</v>
+      </c>
+      <c r="E122" s="2">
+        <v>47.916666666666664</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>250611018</v>
+      </c>
+      <c r="B123" t="s">
+        <v>140</v>
+      </c>
+      <c r="C123" t="s">
+        <v>122</v>
+      </c>
+      <c r="D123" s="2">
+        <v>58.444444444444443</v>
+      </c>
+      <c r="E123" s="2">
+        <v>54.638888888888893</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>250611019</v>
+      </c>
+      <c r="B124" t="s">
+        <v>141</v>
+      </c>
+      <c r="C124" t="s">
+        <v>122</v>
+      </c>
+      <c r="D124" s="2">
+        <v>57.555555555555557</v>
+      </c>
+      <c r="E124" s="2">
+        <v>56.444444444444443</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>250611020</v>
+      </c>
+      <c r="B125" t="s">
+        <v>142</v>
+      </c>
+      <c r="C125" t="s">
+        <v>122</v>
+      </c>
+      <c r="D125" s="2">
+        <v>58</v>
+      </c>
+      <c r="E125" s="2">
+        <v>52.416666666666671</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>250611021</v>
+      </c>
+      <c r="B126" t="s">
+        <v>143</v>
+      </c>
+      <c r="C126" t="s">
+        <v>122</v>
+      </c>
+      <c r="D126" s="2">
+        <v>57.333333333333336</v>
+      </c>
+      <c r="E126" s="2">
+        <v>52.499999999999993</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>250611022</v>
+      </c>
+      <c r="B127" t="s">
+        <v>144</v>
+      </c>
+      <c r="C127" t="s">
+        <v>122</v>
+      </c>
+      <c r="D127" s="2">
+        <v>54.666666666666664</v>
+      </c>
+      <c r="E127" s="2">
+        <v>52.472222222222221</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>250611023</v>
+      </c>
+      <c r="B128" t="s">
+        <v>145</v>
+      </c>
+      <c r="C128" t="s">
+        <v>122</v>
+      </c>
+      <c r="D128" s="2">
+        <v>57.777777777777779</v>
+      </c>
+      <c r="E128" s="2">
+        <v>54.333333333333336</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>250611024</v>
+      </c>
+      <c r="B129" t="s">
+        <v>146</v>
+      </c>
+      <c r="C129" t="s">
+        <v>122</v>
+      </c>
+      <c r="D129" s="2">
+        <v>57.333333333333336</v>
+      </c>
+      <c r="E129" s="2">
+        <v>53.972222222222229</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>250611025</v>
+      </c>
+      <c r="B130" t="s">
+        <v>147</v>
+      </c>
+      <c r="C130" t="s">
+        <v>122</v>
+      </c>
+      <c r="D130" s="2">
+        <v>57.222222222222229</v>
+      </c>
+      <c r="E130" s="2">
+        <v>54.666666666666664</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>250611099</v>
+      </c>
+      <c r="B131" t="s">
+        <v>148</v>
+      </c>
+      <c r="C131" t="s">
+        <v>122</v>
+      </c>
+      <c r="D131" s="2">
+        <v>53.555555555555557</v>
+      </c>
+      <c r="E131" s="2">
+        <v>54.277777777777771</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>250611027</v>
+      </c>
+      <c r="B132" t="s">
+        <v>149</v>
+      </c>
+      <c r="C132" t="s">
+        <v>122</v>
+      </c>
+      <c r="D132" s="2">
+        <v>57.555555555555557</v>
+      </c>
+      <c r="E132" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>250611028</v>
+      </c>
+      <c r="B133" t="s">
+        <v>150</v>
+      </c>
+      <c r="C133" t="s">
+        <v>122</v>
+      </c>
+      <c r="D133" s="2">
+        <v>58</v>
+      </c>
+      <c r="E133" s="2">
+        <v>52.499999999999993</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>250611097</v>
+      </c>
+      <c r="B134" t="s">
+        <v>151</v>
+      </c>
+      <c r="C134" t="s">
+        <v>122</v>
+      </c>
+      <c r="D134" s="2">
+        <v>55.666666666666671</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45.472222222222221</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>250611029</v>
+      </c>
+      <c r="B135" t="s">
+        <v>152</v>
+      </c>
+      <c r="C135" t="s">
+        <v>122</v>
+      </c>
+      <c r="D135" s="2">
+        <v>45.888888888888893</v>
+      </c>
+      <c r="E135" s="2">
+        <v>56.055555555555557</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>250611030</v>
+      </c>
+      <c r="B136" t="s">
+        <v>153</v>
+      </c>
+      <c r="C136" t="s">
+        <v>122</v>
+      </c>
+      <c r="D136" s="2">
+        <v>58.666666666666671</v>
+      </c>
+      <c r="E136" s="2">
+        <v>56.083333333333336</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>250611031</v>
+      </c>
+      <c r="B137" t="s">
+        <v>154</v>
+      </c>
+      <c r="C137" t="s">
+        <v>122</v>
+      </c>
+      <c r="D137" s="2">
+        <v>58.444444444444443</v>
+      </c>
+      <c r="E137" s="2">
+        <v>56.888888888888886</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>250611032</v>
+      </c>
+      <c r="B138" t="s">
+        <v>155</v>
+      </c>
+      <c r="C138" t="s">
+        <v>122</v>
+      </c>
+      <c r="D138" s="2">
+        <v>55.333333333333336</v>
+      </c>
+      <c r="E138" s="2">
+        <v>52.25</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>250611033</v>
+      </c>
+      <c r="B139" t="s">
+        <v>156</v>
+      </c>
+      <c r="C139" t="s">
+        <v>122</v>
+      </c>
+      <c r="D139" s="2">
+        <v>57.111111111111114</v>
+      </c>
+      <c r="E139" s="2">
+        <v>56.465160075329564</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>250611034</v>
+      </c>
+      <c r="B140" t="s">
+        <v>157</v>
+      </c>
+      <c r="C140" t="s">
+        <v>122</v>
+      </c>
+      <c r="D140" s="2">
+        <v>58.666666666666671</v>
+      </c>
+      <c r="E140" s="2">
+        <v>49.583333333333329</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>250611035</v>
+      </c>
+      <c r="B141" t="s">
+        <v>158</v>
+      </c>
+      <c r="C141" t="s">
+        <v>122</v>
+      </c>
+      <c r="D141" s="2">
+        <v>59.111111111111114</v>
+      </c>
+      <c r="E141" s="2">
+        <v>53.833333333333329</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>250611036</v>
+      </c>
+      <c r="B142" t="s">
+        <v>159</v>
+      </c>
+      <c r="C142" t="s">
+        <v>122</v>
+      </c>
+      <c r="D142" s="2">
+        <v>58.666666666666671</v>
+      </c>
+      <c r="E142" s="2">
+        <v>55.250000000000007</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>250611037</v>
+      </c>
+      <c r="B143" t="s">
+        <v>160</v>
+      </c>
+      <c r="C143" t="s">
+        <v>122</v>
+      </c>
+      <c r="D143" s="2">
+        <v>57.333333333333336</v>
+      </c>
+      <c r="E143" s="2">
+        <v>53.194444444444443</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>250611038</v>
+      </c>
+      <c r="B144" t="s">
+        <v>161</v>
+      </c>
+      <c r="C144" t="s">
+        <v>122</v>
+      </c>
+      <c r="D144" s="2">
+        <v>57.555555555555557</v>
+      </c>
+      <c r="E144" s="2">
+        <v>48.777777777777786</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <v>250611039</v>
+      </c>
+      <c r="B145" t="s">
+        <v>162</v>
+      </c>
+      <c r="C145" t="s">
+        <v>122</v>
+      </c>
+      <c r="D145" s="2">
+        <v>58.222222222222221</v>
+      </c>
+      <c r="E145" s="2">
+        <v>58.222222222222221</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>260711041</v>
+      </c>
+      <c r="B146" t="s">
+        <v>163</v>
+      </c>
+      <c r="C146" t="s">
+        <v>73</v>
+      </c>
+      <c r="E146" s="1"/>
+      <c r="K146">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>250611053</v>
+      </c>
+      <c r="B147" t="s">
+        <v>164</v>
+      </c>
+      <c r="C147" t="s">
+        <v>73</v>
+      </c>
+      <c r="K147">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>260711029</v>
+      </c>
+      <c r="B148" t="s">
+        <v>165</v>
+      </c>
+      <c r="C148" t="s">
+        <v>73</v>
+      </c>
+      <c r="K148">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <v>250611041</v>
+      </c>
+      <c r="B149" t="s">
+        <v>166</v>
+      </c>
+      <c r="C149" t="s">
+        <v>73</v>
+      </c>
+      <c r="K149">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <v>260711030</v>
+      </c>
+      <c r="B150" t="s">
+        <v>167</v>
+      </c>
+      <c r="C150" t="s">
+        <v>73</v>
+      </c>
+      <c r="K150">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>260712077</v>
+      </c>
+      <c r="B151" t="s">
+        <v>168</v>
+      </c>
+      <c r="C151" t="s">
+        <v>73</v>
+      </c>
+      <c r="K151">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <v>260711028</v>
+      </c>
+      <c r="B152" t="s">
+        <v>169</v>
+      </c>
+      <c r="C152" t="s">
+        <v>73</v>
+      </c>
+      <c r="K152">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <v>260711035</v>
+      </c>
+      <c r="B153" t="s">
+        <v>170</v>
+      </c>
+      <c r="C153" t="s">
+        <v>73</v>
+      </c>
+      <c r="K153">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <v>260711040</v>
+      </c>
+      <c r="B154" t="s">
+        <v>171</v>
+      </c>
+      <c r="C154" t="s">
+        <v>73</v>
+      </c>
+      <c r="K154">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <v>260713081</v>
+      </c>
+      <c r="B155" t="s">
+        <v>172</v>
+      </c>
+      <c r="C155" t="s">
+        <v>73</v>
+      </c>
+      <c r="K155">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A156">
+        <v>260711039</v>
+      </c>
+      <c r="B156" t="s">
+        <v>173</v>
+      </c>
+      <c r="C156" t="s">
+        <v>73</v>
+      </c>
+      <c r="K156">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A157">
+        <v>260711053</v>
+      </c>
+      <c r="B157" t="s">
+        <v>174</v>
+      </c>
+      <c r="C157" t="s">
+        <v>73</v>
+      </c>
+      <c r="K157">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A158">
+        <v>260711056</v>
+      </c>
+      <c r="B158" t="s">
+        <v>175</v>
+      </c>
+      <c r="C158" t="s">
+        <v>73</v>
+      </c>
+      <c r="K158">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A159">
+        <v>260711058</v>
+      </c>
+      <c r="B159" t="s">
+        <v>176</v>
+      </c>
+      <c r="C159" t="s">
+        <v>73</v>
+      </c>
+      <c r="K159">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A160">
+        <v>260711059</v>
+      </c>
+      <c r="B160" t="s">
+        <v>177</v>
+      </c>
+      <c r="C160" t="s">
+        <v>73</v>
+      </c>
+      <c r="K160">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A161">
+        <v>260713082</v>
+      </c>
+      <c r="B161" t="s">
+        <v>178</v>
+      </c>
+      <c r="C161" t="s">
+        <v>73</v>
+      </c>
+      <c r="K161">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A162">
+        <v>260711032</v>
+      </c>
+      <c r="B162" t="s">
+        <v>179</v>
+      </c>
+      <c r="C162" t="s">
+        <v>73</v>
+      </c>
+      <c r="K162">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A163">
+        <v>260711023</v>
+      </c>
+      <c r="B163" t="s">
+        <v>180</v>
+      </c>
+      <c r="C163" t="s">
+        <v>73</v>
+      </c>
+      <c r="K163">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A164">
+        <v>260711036</v>
+      </c>
+      <c r="B164" t="s">
+        <v>181</v>
+      </c>
+      <c r="C164" t="s">
+        <v>73</v>
+      </c>
+      <c r="K164">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A165">
+        <v>260721100</v>
+      </c>
+      <c r="B165" t="s">
+        <v>182</v>
+      </c>
+      <c r="C165" t="s">
+        <v>73</v>
+      </c>
+      <c r="K165">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A166">
+        <v>260711044</v>
+      </c>
+      <c r="B166" t="s">
+        <v>183</v>
+      </c>
+      <c r="C166" t="s">
+        <v>73</v>
+      </c>
+      <c r="K166">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A167">
+        <v>260721102</v>
+      </c>
+      <c r="B167" t="s">
+        <v>184</v>
+      </c>
+      <c r="C167" t="s">
+        <v>73</v>
+      </c>
+      <c r="K167">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A168">
+        <v>260712076</v>
+      </c>
+      <c r="B168" t="s">
+        <v>185</v>
+      </c>
+      <c r="C168" t="s">
+        <v>73</v>
+      </c>
+      <c r="K168">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A169">
+        <v>260711045</v>
+      </c>
+      <c r="B169" t="s">
+        <v>186</v>
+      </c>
+      <c r="C169" t="s">
+        <v>73</v>
+      </c>
+      <c r="K169">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A170">
+        <v>260711046</v>
+      </c>
+      <c r="B170" t="s">
+        <v>187</v>
+      </c>
+      <c r="C170" t="s">
+        <v>73</v>
+      </c>
+      <c r="K170">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A171">
+        <v>260711049</v>
+      </c>
+      <c r="B171" t="s">
+        <v>188</v>
+      </c>
+      <c r="C171" t="s">
+        <v>73</v>
+      </c>
+      <c r="K171">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A172">
+        <v>250611080</v>
+      </c>
+      <c r="B172" t="s">
+        <v>189</v>
+      </c>
+      <c r="C172" t="s">
+        <v>73</v>
+      </c>
+      <c r="K172">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A173">
+        <v>260711050</v>
+      </c>
+      <c r="B173" t="s">
+        <v>190</v>
+      </c>
+      <c r="C173" t="s">
+        <v>73</v>
+      </c>
+      <c r="K173">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A174">
+        <v>260711031</v>
+      </c>
+      <c r="B174" t="s">
+        <v>191</v>
+      </c>
+      <c r="C174" t="s">
+        <v>73</v>
+      </c>
+      <c r="K174">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A175">
+        <v>260711024</v>
+      </c>
+      <c r="B175" t="s">
+        <v>192</v>
+      </c>
+      <c r="C175" t="s">
+        <v>73</v>
+      </c>
+      <c r="K175">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A176">
+        <v>260711025</v>
+      </c>
+      <c r="B176" t="s">
+        <v>193</v>
+      </c>
+      <c r="C176" t="s">
+        <v>73</v>
+      </c>
+      <c r="K176">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A177">
+        <v>260711027</v>
+      </c>
+      <c r="B177" t="s">
+        <v>194</v>
+      </c>
+      <c r="C177" t="s">
+        <v>73</v>
+      </c>
+      <c r="K177">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A178">
+        <v>260712075</v>
+      </c>
+      <c r="B178" t="s">
+        <v>195</v>
+      </c>
+      <c r="C178" t="s">
+        <v>73</v>
+      </c>
+      <c r="K178">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A179">
+        <v>260721104</v>
+      </c>
+      <c r="B179" t="s">
+        <v>196</v>
+      </c>
+      <c r="C179" t="s">
+        <v>73</v>
+      </c>
+      <c r="K179">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A180">
+        <v>260711042</v>
+      </c>
+      <c r="B180" t="s">
+        <v>197</v>
+      </c>
+      <c r="C180" t="s">
+        <v>73</v>
+      </c>
+      <c r="K180">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A181">
+        <v>250611067</v>
+      </c>
+      <c r="B181" t="s">
+        <v>198</v>
+      </c>
+      <c r="C181" t="s">
+        <v>73</v>
+      </c>
+      <c r="K181">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A182">
+        <v>260711038</v>
+      </c>
+      <c r="B182" t="s">
+        <v>199</v>
+      </c>
+      <c r="C182" t="s">
+        <v>73</v>
+      </c>
+      <c r="K182">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A183">
+        <v>260711043</v>
+      </c>
+      <c r="B183" t="s">
+        <v>200</v>
+      </c>
+      <c r="C183" t="s">
+        <v>73</v>
+      </c>
+      <c r="K183">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A184">
+        <v>260711033</v>
+      </c>
+      <c r="B184" t="s">
+        <v>201</v>
+      </c>
+      <c r="C184" t="s">
+        <v>73</v>
+      </c>
+      <c r="K184">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A185">
+        <v>260721103</v>
+      </c>
+      <c r="B185" t="s">
+        <v>202</v>
+      </c>
+      <c r="C185" t="s">
+        <v>73</v>
+      </c>
+      <c r="K185">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A186">
+        <v>260711061</v>
+      </c>
+      <c r="B186" t="s">
+        <v>203</v>
+      </c>
+      <c r="C186" t="s">
+        <v>73</v>
+      </c>
+      <c r="K186">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A187">
+        <v>260711054</v>
+      </c>
+      <c r="B187" t="s">
+        <v>204</v>
+      </c>
+      <c r="C187" t="s">
+        <v>73</v>
+      </c>
+      <c r="K187">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A188">
+        <v>260711055</v>
+      </c>
+      <c r="B188" t="s">
+        <v>205</v>
+      </c>
+      <c r="C188" t="s">
+        <v>73</v>
+      </c>
+      <c r="K188">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A189">
+        <v>260711057</v>
+      </c>
+      <c r="B189" t="s">
+        <v>206</v>
+      </c>
+      <c r="C189" t="s">
+        <v>73</v>
+      </c>
+      <c r="K189">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A190">
+        <v>260711060</v>
+      </c>
+      <c r="B190" t="s">
+        <v>207</v>
+      </c>
+      <c r="C190" t="s">
+        <v>73</v>
+      </c>
+      <c r="K190">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A191">
+        <v>260711034</v>
+      </c>
+      <c r="B191" t="s">
+        <v>208</v>
+      </c>
+      <c r="C191" t="s">
+        <v>73</v>
+      </c>
+      <c r="K191">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A192">
+        <v>260721099</v>
+      </c>
+      <c r="B192" t="s">
+        <v>209</v>
+      </c>
+      <c r="C192" t="s">
+        <v>73</v>
+      </c>
+      <c r="K192">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A193">
+        <v>260711026</v>
+      </c>
+      <c r="B193" t="s">
+        <v>210</v>
+      </c>
+      <c r="C193" t="s">
+        <v>73</v>
+      </c>
+      <c r="K193">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A194">
+        <v>260711037</v>
+      </c>
+      <c r="B194" t="s">
+        <v>211</v>
+      </c>
+      <c r="C194" t="s">
+        <v>73</v>
+      </c>
+      <c r="K194">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A195">
+        <v>260721101</v>
+      </c>
+      <c r="B195" t="s">
+        <v>212</v>
+      </c>
+      <c r="C195" t="s">
+        <v>73</v>
+      </c>
+      <c r="K195">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A196">
+        <v>260711047</v>
+      </c>
+      <c r="B196" t="s">
+        <v>213</v>
+      </c>
+      <c r="C196" t="s">
+        <v>73</v>
+      </c>
+      <c r="K196">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A197">
+        <v>260711048</v>
+      </c>
+      <c r="B197" t="s">
+        <v>214</v>
+      </c>
+      <c r="C197" t="s">
+        <v>73</v>
+      </c>
+      <c r="K197">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A198">
+        <v>260711052</v>
+      </c>
+      <c r="B198" t="s">
+        <v>215</v>
+      </c>
+      <c r="C198" t="s">
+        <v>73</v>
+      </c>
+      <c r="K198">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A199">
+        <v>260711051</v>
+      </c>
+      <c r="B199" t="s">
+        <v>216</v>
+      </c>
+      <c r="C199" t="s">
+        <v>73</v>
+      </c>
+      <c r="K199">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
